--- a/app/src/main/assets/Pipistrelli 2024.xlsx
+++ b/app/src/main/assets/Pipistrelli 2024.xlsx
@@ -16,9 +16,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -49,9 +48,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -498,7 +498,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>45303</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -544,7 +544,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
         <v>45.6413213</v>
       </c>
@@ -563,7 +562,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>45334</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -576,7 +575,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>San Lazzaro</t>
@@ -605,7 +603,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
         <v>45.7483873</v>
       </c>
@@ -624,7 +621,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>45371</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -637,7 +634,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -666,7 +662,6 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
         <v>45.6348591</v>
       </c>
@@ -685,7 +680,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>45385</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -731,7 +726,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
         <v>45.6348591</v>
       </c>
@@ -750,7 +744,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>45388</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -796,7 +790,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
         <v>45.6111057</v>
       </c>
@@ -815,7 +808,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>45389</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -861,7 +854,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
         <v>45.6111057</v>
       </c>
@@ -880,7 +872,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>45395</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -926,7 +918,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
         <v>45.772805</v>
       </c>
@@ -945,7 +936,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>45397</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -991,7 +982,6 @@
           <t>in degenza</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
         <v>45.5084288</v>
       </c>
@@ -1010,7 +1000,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>45398</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -1023,7 +1013,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t xml:space="preserve">Grisignano </t>
@@ -1052,18 +1041,15 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
         <v>44.1821589</v>
       </c>
       <c r="M10" t="n">
         <v>12.0321866</v>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>45422</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -1076,7 +1062,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -1105,7 +1090,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
         <v>45.6348591</v>
       </c>
@@ -1124,7 +1108,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>45423</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -1170,7 +1154,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
         <v>45.8461561</v>
       </c>
@@ -1189,7 +1172,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>45429</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -1235,7 +1218,6 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
         <v>45.7669109</v>
       </c>
@@ -1254,7 +1236,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>45429</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -1267,7 +1249,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>Viale Sant'Agostino</t>
@@ -1296,7 +1277,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
         <v>45.5276929</v>
       </c>
@@ -1315,7 +1295,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>45434</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -1361,18 +1341,15 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
         <v>45.5063765</v>
       </c>
       <c r="M15" t="n">
         <v>11.5093217</v>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>45436</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -1385,7 +1362,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>Viale della Pace</t>
@@ -1414,7 +1390,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
         <v>45.5419084</v>
       </c>
@@ -1433,7 +1408,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>45437</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -1479,7 +1454,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
         <v>45.8066913</v>
       </c>
@@ -1498,7 +1472,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>45446</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -1511,7 +1485,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>Lago di Fimon</t>
@@ -1540,18 +1513,15 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
         <v>45.4711586</v>
       </c>
       <c r="M18" t="n">
         <v>11.5436596</v>
       </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>45446</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -1564,7 +1534,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>Lago di Fimon</t>
@@ -1593,18 +1562,15 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
         <v>45.4711586</v>
       </c>
       <c r="M19" t="n">
         <v>11.5436596</v>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>45460</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -1617,7 +1583,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>Arcugnano</t>
@@ -1646,7 +1611,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
         <v>45.5004723</v>
       </c>
@@ -1665,7 +1629,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>45460</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -1678,7 +1642,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>Via Col d'Echele 3</t>
@@ -1707,7 +1670,6 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
       <c r="L21" t="n">
         <v>45.5561119</v>
       </c>
@@ -1726,7 +1688,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>45460</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -1739,7 +1701,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>Grisignano</t>
@@ -1768,18 +1729,15 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
       <c r="L22" t="n">
         <v>44.1821589</v>
       </c>
       <c r="M22" t="n">
         <v>12.0321866</v>
       </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>45462</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -1792,7 +1750,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>Arzignano</t>
@@ -1821,7 +1778,6 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
       <c r="L23" t="n">
         <v>45.519292</v>
       </c>
@@ -1840,7 +1796,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>45462</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -1853,7 +1809,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t xml:space="preserve">Castegnero </t>
@@ -1882,7 +1837,6 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
       <c r="L24" t="n">
         <v>45.4424748</v>
       </c>
@@ -1901,7 +1855,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>45462</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -1914,7 +1868,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t xml:space="preserve">Castegnero </t>
@@ -1943,7 +1896,6 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
       <c r="L25" t="n">
         <v>45.4424748</v>
       </c>
@@ -1962,7 +1914,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>45462</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -1975,7 +1927,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>Verona</t>
@@ -2004,7 +1955,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
       <c r="L26" t="n">
         <v>45.4424977</v>
       </c>
@@ -2023,7 +1973,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>45462</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -2036,7 +1986,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>Schio</t>
@@ -2086,7 +2035,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>45463</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -2099,7 +2048,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>Thiene</t>
@@ -2128,7 +2076,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
       <c r="L28" t="n">
         <v>45.7059893</v>
       </c>
@@ -2147,7 +2094,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>45464</v>
       </c>
       <c r="B29" t="inlineStr">
@@ -2193,7 +2140,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
       <c r="L29" t="n">
         <v>45.5951803</v>
       </c>
@@ -2212,7 +2158,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>45464</v>
       </c>
       <c r="B30" t="inlineStr">
@@ -2225,7 +2171,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>Schio</t>
@@ -2254,7 +2199,6 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
       <c r="L30" t="n">
         <v>45.7113511</v>
       </c>
@@ -2273,7 +2217,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>45465</v>
       </c>
       <c r="B31" t="inlineStr">
@@ -2286,7 +2230,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>Piovene Rocchette</t>
@@ -2315,7 +2258,6 @@
           <t>in degenza</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
       <c r="L31" t="n">
         <v>45.7588257</v>
       </c>
@@ -2334,7 +2276,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>45466</v>
       </c>
       <c r="B32" t="inlineStr">
@@ -2347,7 +2289,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>Costozza</t>
@@ -2397,7 +2338,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>45467</v>
       </c>
       <c r="B33" t="inlineStr">
@@ -2410,7 +2351,6 @@
           <t>Pipistrellus pipistrellus</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>via giustiniani 79</t>
@@ -2439,7 +2379,6 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
       <c r="L33" t="n">
         <v>45.5056451</v>
       </c>
@@ -2458,7 +2397,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>45467</v>
       </c>
       <c r="B34" t="inlineStr">
@@ -2471,7 +2410,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t xml:space="preserve">montecchio </t>
@@ -2521,7 +2459,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>45467</v>
       </c>
       <c r="B35" t="inlineStr">
@@ -2567,7 +2505,6 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
       <c r="L35" t="n">
         <v>45.5220266</v>
       </c>
@@ -2586,7 +2523,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>45467</v>
       </c>
       <c r="B36" t="inlineStr">
@@ -2632,7 +2569,6 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
       <c r="L36" t="n">
         <v>45.5220266</v>
       </c>
@@ -2651,7 +2587,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>45467</v>
       </c>
       <c r="B37" t="inlineStr">
@@ -2664,7 +2600,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>Verona</t>
@@ -2693,7 +2628,6 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
       <c r="L37" t="n">
         <v>45.4424977</v>
       </c>
@@ -2712,7 +2646,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>45467</v>
       </c>
       <c r="B38" t="inlineStr">
@@ -2725,7 +2659,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>Corso Santi Felice e Fortunato</t>
@@ -2763,11 +2696,9 @@
       <c r="M38" t="n">
         <v>11.5352125</v>
       </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>45467</v>
       </c>
       <c r="B39" t="inlineStr">
@@ -2780,7 +2711,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
           <t>Via Marchetti, 14</t>
@@ -2830,7 +2760,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>45467</v>
       </c>
       <c r="B40" t="inlineStr">
@@ -2843,7 +2773,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>Costozza</t>
@@ -2872,18 +2801,15 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
       <c r="L40" t="n">
         <v>45.4709699</v>
       </c>
       <c r="M40" t="n">
         <v>11.6014322</v>
       </c>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>45468</v>
       </c>
       <c r="B41" t="inlineStr">
@@ -2896,7 +2822,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>Via Leonardo da Vinci, 8</t>
@@ -2925,7 +2850,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
       <c r="L41" t="n">
         <v>45.6577391</v>
       </c>
@@ -2944,7 +2868,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>45468</v>
       </c>
       <c r="B42" t="inlineStr">
@@ -2957,7 +2881,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>Pove del Grappa</t>
@@ -2986,7 +2909,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
       <c r="L42" t="n">
         <v>45.7991169</v>
       </c>
@@ -3005,7 +2927,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>45468</v>
       </c>
       <c r="B43" t="inlineStr">
@@ -3051,7 +2973,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
       <c r="L43" t="n">
         <v>45.697721</v>
       </c>
@@ -3070,7 +2991,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>45468</v>
       </c>
       <c r="B44" t="inlineStr">
@@ -3083,7 +3004,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
           <t>Costozza</t>
@@ -3121,11 +3041,9 @@
       <c r="M44" t="n">
         <v>11.6014322</v>
       </c>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>45469</v>
       </c>
       <c r="B45" t="inlineStr">
@@ -3138,7 +3056,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>Via Giuseppe Roi, 13</t>
@@ -3167,7 +3084,6 @@
           <t>in degenza</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
       <c r="L45" t="n">
         <v>45.4558599</v>
       </c>
@@ -3186,7 +3102,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>45470</v>
       </c>
       <c r="B46" t="inlineStr">
@@ -3199,7 +3115,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
           <t>Via Piave 23</t>
@@ -3228,7 +3143,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
       <c r="L46" t="n">
         <v>45.6180489</v>
       </c>
@@ -3247,7 +3161,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>45470</v>
       </c>
       <c r="B47" t="inlineStr">
@@ -3260,7 +3174,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
           <t>Via Don A. Ziliotto, 24</t>
@@ -3279,13 +3192,11 @@
       <c r="H47" t="n">
         <v>1</v>
       </c>
-      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>liberato</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
       <c r="L47" t="n">
         <v>45.7059893</v>
       </c>
@@ -3304,7 +3215,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>45470</v>
       </c>
       <c r="B48" t="inlineStr">
@@ -3317,7 +3228,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -3367,7 +3277,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>45470</v>
       </c>
       <c r="B49" t="inlineStr">
@@ -3380,7 +3290,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t>Bassano del Grappa, Vicenza</t>
@@ -3409,7 +3318,6 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
       <c r="L49" t="n">
         <v>45.7669109</v>
       </c>
@@ -3421,10 +3329,9 @@
           <t>VI</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>45471</v>
       </c>
       <c r="B50" t="inlineStr">
@@ -3437,7 +3344,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -3487,7 +3393,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>45471</v>
       </c>
       <c r="B51" t="inlineStr">
@@ -3500,7 +3406,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
           <t>Via Scomazzoni 12A</t>
@@ -3550,7 +3455,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>45471</v>
       </c>
       <c r="B52" t="inlineStr">
@@ -3563,7 +3468,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
           <t>Via Monsinior Pertile</t>
@@ -3592,7 +3496,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
       <c r="L52" t="n">
         <v>45.7059893</v>
       </c>
@@ -3611,7 +3514,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>45471</v>
       </c>
       <c r="B53" t="inlineStr">
@@ -3624,7 +3527,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
           <t>Via Nicolò Tommaso 12</t>
@@ -3653,7 +3555,6 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
       <c r="L53" t="n">
         <v>45.6861778</v>
       </c>
@@ -3672,7 +3573,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>45471</v>
       </c>
       <c r="B54" t="inlineStr">
@@ -3685,7 +3586,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
           <t>Via Andrea Boccherini 23</t>
@@ -3735,7 +3635,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45471</v>
       </c>
       <c r="B55" t="inlineStr">
@@ -3748,7 +3648,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
           <t>Via Monsignor Pertile</t>
@@ -3777,7 +3676,6 @@
           <t>in degenza</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
       <c r="L55" t="n">
         <v>45.7059893</v>
       </c>
@@ -3796,7 +3694,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45471</v>
       </c>
       <c r="B56" t="inlineStr">
@@ -3842,7 +3740,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
       <c r="L56" t="n">
         <v>45.5502771</v>
       </c>
@@ -3861,7 +3758,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45472</v>
       </c>
       <c r="B57" t="inlineStr">
@@ -3874,7 +3771,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
           <t>Via Lago di Tovel, 43</t>
@@ -3924,7 +3820,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45472</v>
       </c>
       <c r="B58" t="inlineStr">
@@ -3937,7 +3833,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
           <t>Monselice</t>
@@ -3987,7 +3882,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45472</v>
       </c>
       <c r="B59" t="inlineStr">
@@ -4000,7 +3895,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
           <t>Thiene</t>
@@ -4050,7 +3944,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45472</v>
       </c>
       <c r="B60" t="inlineStr">
@@ -4063,7 +3957,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
           <t>Grisignano</t>
@@ -4101,11 +3994,9 @@
       <c r="M60" t="n">
         <v>12.0321866</v>
       </c>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B61" t="inlineStr">
@@ -4118,7 +4009,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
           <t>brogliano</t>
@@ -4147,7 +4037,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
       <c r="L61" t="n">
         <v>45.5887862</v>
       </c>
@@ -4166,7 +4055,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B62" t="inlineStr">
@@ -4179,7 +4068,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
           <t xml:space="preserve">Isola Vicentina </t>
@@ -4208,7 +4096,6 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
       <c r="L62" t="n">
         <v>45.6286685</v>
       </c>
@@ -4227,7 +4114,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B63" t="inlineStr">
@@ -4240,7 +4127,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
           <t>Marostica</t>
@@ -4269,7 +4155,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
       <c r="L63" t="n">
         <v>45.7453924</v>
       </c>
@@ -4288,7 +4173,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="B64" t="inlineStr">
@@ -4301,7 +4186,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t>Sovizzo</t>
@@ -4330,7 +4214,6 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
       <c r="L64" t="n">
         <v>45.5280283</v>
       </c>
@@ -4349,7 +4232,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="B65" t="inlineStr">
@@ -4362,7 +4245,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
           <t>Sovizzo</t>
@@ -4391,7 +4273,6 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
       <c r="L65" t="n">
         <v>45.5280283</v>
       </c>
@@ -4410,7 +4291,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="B66" t="inlineStr">
@@ -4423,7 +4304,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
           <t>Altavilla vicentina</t>
@@ -4473,7 +4353,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="B67" t="inlineStr">
@@ -4486,7 +4366,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
           <t>Bressanvido</t>
@@ -4515,7 +4394,6 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
       <c r="L67" t="n">
         <v>45.6459759</v>
       </c>
@@ -4534,7 +4412,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45475</v>
       </c>
       <c r="B68" t="inlineStr">
@@ -4547,7 +4425,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
           <t>Treviso</t>
@@ -4576,7 +4453,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
       <c r="L68" t="n">
         <v>45.8066913</v>
       </c>
@@ -4595,7 +4471,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45475</v>
       </c>
       <c r="B69" t="inlineStr">
@@ -4608,7 +4484,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
           <t>Via Jacopo da Ponte</t>
@@ -4637,7 +4512,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
       <c r="L69" t="n">
         <v>45.6230008</v>
       </c>
@@ -4656,7 +4530,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="B70" t="inlineStr">
@@ -4669,7 +4543,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
           <t>Via Monsignor Pertile</t>
@@ -4698,7 +4571,6 @@
           <t>in degenza</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
       <c r="L70" t="n">
         <v>45.7059893</v>
       </c>
@@ -4717,7 +4589,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45475</v>
       </c>
       <c r="B71" t="inlineStr">
@@ -4730,7 +4602,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
           <t>Schio</t>
@@ -4759,7 +4630,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
       <c r="L71" t="n">
         <v>45.7113511</v>
       </c>
@@ -4778,7 +4648,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>45475</v>
       </c>
       <c r="B72" t="inlineStr">
@@ -4791,7 +4661,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
           <t>via bologna 33</t>
@@ -4820,7 +4689,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
       <c r="L72" t="n">
         <v>45.515467</v>
       </c>
@@ -4839,7 +4707,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>45476</v>
       </c>
       <c r="B73" t="inlineStr">
@@ -4852,7 +4720,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
           <t>Arcugnano</t>
@@ -4881,7 +4748,6 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
       <c r="L73" t="n">
         <v>45.5004723</v>
       </c>
@@ -4900,7 +4766,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>45478</v>
       </c>
       <c r="B74" t="inlineStr">
@@ -4913,7 +4779,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
           <t>Viale della Pace</t>
@@ -4942,7 +4807,6 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
       <c r="L74" t="n">
         <v>45.5419084</v>
       </c>
@@ -4961,7 +4825,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>45479</v>
       </c>
       <c r="B75" t="inlineStr">
@@ -4974,7 +4838,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
           <t>vicenza</t>
@@ -5003,7 +4866,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
       <c r="L75" t="n">
         <v>45.6348591</v>
       </c>
@@ -5022,7 +4884,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>45481</v>
       </c>
       <c r="B76" t="inlineStr">
@@ -5035,7 +4897,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
           <t>Camisano</t>
@@ -5064,7 +4925,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
       <c r="L76" t="n">
         <v>45.443275</v>
       </c>
@@ -5083,7 +4943,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>45481</v>
       </c>
       <c r="B77" t="inlineStr">
@@ -5096,7 +4956,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
           <t>Strada statale Pasubio</t>
@@ -5146,7 +5005,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>45481</v>
       </c>
       <c r="B78" t="inlineStr">
@@ -5159,7 +5018,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
           <t>Valdagno</t>
@@ -5209,7 +5067,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>45481</v>
       </c>
       <c r="B79" t="inlineStr">
@@ -5222,7 +5080,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
           <t>Via canestrello 8</t>
@@ -5251,7 +5108,6 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
       <c r="L79" t="n">
         <v>45.5548982</v>
       </c>
@@ -5270,7 +5126,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>45481</v>
       </c>
       <c r="B80" t="inlineStr">
@@ -5283,7 +5139,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
           <t>Via gioranzan 13</t>
@@ -5312,7 +5167,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
       <c r="L80" t="n">
         <v>45.5208426</v>
       </c>
@@ -5331,7 +5185,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>45482</v>
       </c>
       <c r="B81" t="inlineStr">
@@ -5344,7 +5198,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
           <t>Via Carlesse 55</t>
@@ -5373,7 +5226,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
       <c r="L81" t="n">
         <v>45.636598</v>
       </c>
@@ -5392,7 +5244,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>45482</v>
       </c>
       <c r="B82" t="inlineStr">
@@ -5405,7 +5257,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
           <t>Cornedo Vicentino</t>
@@ -5455,7 +5306,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>45482</v>
       </c>
       <c r="B83" t="inlineStr">
@@ -5501,7 +5352,6 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
       <c r="L83" t="n">
         <v>45.3317317</v>
       </c>
@@ -5520,7 +5370,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>45484</v>
       </c>
       <c r="B84" t="inlineStr">
@@ -5533,7 +5383,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
           <t>Santorso</t>
@@ -5583,7 +5432,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>45485</v>
       </c>
       <c r="B85" t="inlineStr">
@@ -5596,7 +5445,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
           <t>Povolaro</t>
@@ -5646,7 +5494,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>45486</v>
       </c>
       <c r="B86" t="inlineStr">
@@ -5659,7 +5507,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
           <t>Longare</t>
@@ -5688,7 +5535,6 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
       <c r="L86" t="n">
         <v>45.4746344</v>
       </c>
@@ -5707,7 +5553,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>45488</v>
       </c>
       <c r="B87" t="inlineStr">
@@ -5720,7 +5566,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
           <t>Via Oreficeria, 16</t>
@@ -5749,7 +5594,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
       <c r="L87" t="n">
         <v>45.5288639</v>
       </c>
@@ -5768,7 +5612,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>45490</v>
       </c>
       <c r="B88" t="inlineStr">
@@ -5781,7 +5625,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
           <t>Malga monte Asolone</t>
@@ -5810,7 +5653,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
       <c r="L88" t="n">
         <v>45.8672973</v>
       </c>
@@ -5829,7 +5671,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>45490</v>
       </c>
       <c r="B89" t="inlineStr">
@@ -5842,7 +5684,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
           <t>Via Aurelio dall'acqua 119</t>
@@ -5871,7 +5712,6 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
       <c r="L89" t="n">
         <v>45.5678021</v>
       </c>
@@ -5890,7 +5730,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>45490</v>
       </c>
       <c r="B90" t="inlineStr">
@@ -5903,7 +5743,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
           <t>Via Tecchio</t>
@@ -5953,7 +5792,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>45490</v>
       </c>
       <c r="B91" t="inlineStr">
@@ -5966,7 +5805,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
           <t>Via Marnian</t>
@@ -5995,7 +5833,6 @@
           <t>in degenza</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
       <c r="L91" t="n">
         <v>45.7669109</v>
       </c>
@@ -6014,7 +5851,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>45492</v>
       </c>
       <c r="B92" t="inlineStr">
@@ -6027,7 +5864,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
           <t>Via mottarella 17</t>
@@ -6056,7 +5892,6 @@
           <t>in degenza</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
       <c r="L92" t="n">
         <v>45.3446852</v>
       </c>
@@ -6075,7 +5910,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>45494</v>
       </c>
       <c r="B93" t="inlineStr">
@@ -6088,7 +5923,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
           <t>Vicolo xx settembre 9</t>
@@ -6117,7 +5951,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
       <c r="L93" t="n">
         <v>45.7683298</v>
       </c>
@@ -6136,7 +5969,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>45497</v>
       </c>
       <c r="B94" t="inlineStr">
@@ -6149,7 +5982,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
           <t>Bassano</t>
@@ -6192,10 +6024,9 @@
           <t>VI</t>
         </is>
       </c>
-      <c r="O94" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>45499</v>
       </c>
       <c r="B95" t="inlineStr">
@@ -6208,7 +6039,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
           <t>Calvene</t>
@@ -6237,7 +6067,6 @@
           <t>in degenza</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
       <c r="L95" t="n">
         <v>45.7659086</v>
       </c>
@@ -6256,7 +6085,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>45502</v>
       </c>
       <c r="B96" t="inlineStr">
@@ -6269,7 +6098,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
           <t>Lusiana</t>
@@ -6298,18 +6126,15 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
       <c r="L96" t="n">
         <v>45.7851934</v>
       </c>
       <c r="M96" t="n">
         <v>11.576369</v>
       </c>
-      <c r="N96" t="inlineStr"/>
-      <c r="O96" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>45503</v>
       </c>
       <c r="B97" t="inlineStr">
@@ -6322,7 +6147,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
           <t>Via dei laghi 20</t>
@@ -6351,7 +6175,6 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
       <c r="L97" t="n">
         <v>45.5211218</v>
       </c>
@@ -6363,10 +6186,9 @@
           <t>VI</t>
         </is>
       </c>
-      <c r="O97" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>45503</v>
       </c>
       <c r="B98" t="inlineStr">
@@ -6379,7 +6201,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
           <t>Via Barco 21</t>
@@ -6408,7 +6229,6 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
       <c r="L98" t="n">
         <v>45.6077149</v>
       </c>
@@ -6427,7 +6247,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="B99" t="inlineStr">
@@ -6440,7 +6260,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
           <t>Via odone 18 a</t>
@@ -6469,7 +6288,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
       <c r="L99" t="n">
         <v>47.2186371</v>
       </c>
@@ -6488,7 +6306,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="B100" t="inlineStr">
@@ -6534,7 +6352,6 @@
           <t>in degenza</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
       <c r="L100" t="n">
         <v>45.7962374</v>
       </c>
@@ -6553,7 +6370,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>45511</v>
       </c>
       <c r="B101" t="inlineStr">
@@ -6566,7 +6383,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
           <t>Valdagno</t>
@@ -6595,7 +6411,6 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
       <c r="L101" t="n">
         <v>45.6413213</v>
       </c>
@@ -6614,7 +6429,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>45520</v>
       </c>
       <c r="B102" t="inlineStr">
@@ -6627,7 +6442,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
           <t>Via monte oro 33</t>
@@ -6656,7 +6470,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
       <c r="L102" t="n">
         <v>45.7942477</v>
       </c>
@@ -6675,7 +6488,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>45525</v>
       </c>
       <c r="B103" t="inlineStr">
@@ -6688,7 +6501,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
           <t>Valdagno</t>
@@ -6717,7 +6529,6 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
       <c r="L103" t="n">
         <v>45.6413213</v>
       </c>
@@ -6736,7 +6547,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>45533</v>
       </c>
       <c r="B104" t="inlineStr">
@@ -6782,7 +6593,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
       <c r="L104" t="n">
         <v>45.7669109</v>
       </c>
@@ -6801,7 +6611,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>45533</v>
       </c>
       <c r="B105" t="inlineStr">
@@ -6814,7 +6624,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
           <t>Via Marco Marinoni 28</t>
@@ -6864,7 +6673,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>45537</v>
       </c>
       <c r="B106" t="inlineStr">
@@ -6877,7 +6686,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -6906,7 +6714,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
       <c r="L106" t="n">
         <v>45.6348591</v>
       </c>
@@ -6925,7 +6732,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>45540</v>
       </c>
       <c r="B107" t="inlineStr">
@@ -6938,7 +6745,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
           <t>Dueville</t>
@@ -6967,7 +6773,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
       <c r="L107" t="n">
         <v>45.6355174</v>
       </c>
@@ -6986,7 +6791,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>45544</v>
       </c>
       <c r="B108" t="inlineStr">
@@ -6999,7 +6804,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
           <t>Via Oreficeria, 16</t>
@@ -7028,7 +6832,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
       <c r="L108" t="n">
         <v>45.5288639</v>
       </c>
@@ -7047,7 +6850,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>45544</v>
       </c>
       <c r="B109" t="inlineStr">
@@ -7060,7 +6863,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
           <t>Arcugnano</t>
@@ -7089,7 +6891,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
       <c r="L109" t="n">
         <v>45.5004723</v>
       </c>
@@ -7108,7 +6909,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>45544</v>
       </c>
       <c r="B110" t="inlineStr">
@@ -7121,7 +6922,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
           <t>Via Monte Pasubio 96a</t>
@@ -7150,7 +6950,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
       <c r="L110" t="n">
         <v>45.7209364</v>
       </c>
@@ -7169,7 +6968,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>45547</v>
       </c>
       <c r="B111" t="inlineStr">
@@ -7215,7 +7014,6 @@
           <t>in degenza</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
       <c r="L111" t="n">
         <v>45.5269679</v>
       </c>
@@ -7234,7 +7032,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>45552</v>
       </c>
       <c r="B112" t="inlineStr">
@@ -7247,7 +7045,6 @@
           <t>Plecotus sp.</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
           <t xml:space="preserve">Bassano del Grappa </t>
@@ -7276,7 +7073,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
       <c r="L112" t="n">
         <v>45.7669109</v>
       </c>
@@ -7295,7 +7091,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>45553</v>
       </c>
       <c r="B113" t="inlineStr">
@@ -7308,7 +7104,6 @@
           <t>Plecotus Macrobullaris</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
           <t>Santorso</t>
@@ -7337,7 +7132,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
       <c r="L113" t="n">
         <v>45.7372986</v>
       </c>
@@ -7356,7 +7150,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>45556</v>
       </c>
       <c r="B114" t="inlineStr">
@@ -7402,7 +7196,6 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
       <c r="L114" t="n">
         <v>45.5419084</v>
       </c>
@@ -7421,7 +7214,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>45557</v>
       </c>
       <c r="B115" t="inlineStr">
@@ -7434,7 +7227,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
           <t>Via San Niccolò 53</t>
@@ -7453,24 +7245,20 @@
       <c r="H115" t="n">
         <v>1</v>
       </c>
-      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
           <t>in degenza</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
       <c r="L115" t="n">
         <v>45.453842</v>
       </c>
       <c r="M115" t="n">
         <v>11.5551735</v>
       </c>
-      <c r="N115" t="inlineStr"/>
-      <c r="O115" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>45558</v>
       </c>
       <c r="B116" t="inlineStr">
@@ -7483,7 +7271,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
           <t xml:space="preserve">Dueville </t>
@@ -7512,7 +7299,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
       <c r="L116" t="n">
         <v>45.6355174</v>
       </c>
@@ -7531,7 +7317,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>45560</v>
       </c>
       <c r="B117" t="inlineStr">
@@ -7577,7 +7363,6 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
       <c r="L117" t="n">
         <v>45.7059893</v>
       </c>
@@ -7596,7 +7381,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>45562</v>
       </c>
       <c r="B118" t="inlineStr">
@@ -7642,7 +7427,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
       <c r="L118" t="n">
         <v>45.6073305</v>
       </c>
@@ -7661,7 +7445,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B119" t="inlineStr">
@@ -7707,7 +7491,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
       <c r="L119" t="n">
         <v>45.7669109</v>
       </c>
@@ -7726,7 +7509,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>45566</v>
       </c>
       <c r="B120" t="inlineStr">
@@ -7739,7 +7522,6 @@
           <t>Pipistrellus pipistrellus</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -7768,7 +7550,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
       <c r="L120" t="n">
         <v>45.6348591</v>
       </c>
@@ -7787,7 +7568,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>45572</v>
       </c>
       <c r="B121" t="inlineStr">
@@ -7800,7 +7581,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
           <t>Via lago di fimon 63</t>
@@ -7829,7 +7609,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
       <c r="L121" t="n">
         <v>45.4544981</v>
       </c>
@@ -7848,7 +7627,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>45574</v>
       </c>
       <c r="B122" t="inlineStr">
@@ -7861,7 +7640,6 @@
           <t>Tadarida teniotis</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -7890,7 +7668,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
       <c r="L122" t="n">
         <v>45.6348591</v>
       </c>
@@ -7909,7 +7686,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>45583</v>
       </c>
       <c r="B123" t="inlineStr">
@@ -7922,7 +7699,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
           <t>Lonigo</t>
@@ -7951,7 +7727,6 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
       <c r="L123" t="n">
         <v>45.3881155</v>
       </c>
@@ -7970,7 +7745,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>45584</v>
       </c>
       <c r="B124" t="inlineStr">
@@ -8016,7 +7791,6 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
       <c r="L124" t="n">
         <v>45.7113511</v>
       </c>
@@ -8035,7 +7809,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B125" t="inlineStr">
@@ -8048,7 +7822,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -8077,7 +7850,6 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
       <c r="L125" t="n">
         <v>45.6348591</v>
       </c>
@@ -8096,7 +7868,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>45591</v>
       </c>
       <c r="B126" t="inlineStr">
@@ -8142,7 +7914,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
       <c r="L126" t="n">
         <v>45.5422473</v>
       </c>
@@ -8161,7 +7932,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>45599</v>
       </c>
       <c r="B127" t="inlineStr">
@@ -8174,7 +7945,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -8203,7 +7973,6 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
       <c r="L127" t="n">
         <v>45.6348591</v>
       </c>
@@ -8222,7 +7991,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>45607</v>
       </c>
       <c r="B128" t="inlineStr">
@@ -8268,7 +8037,6 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
       <c r="L128" t="n">
         <v>45.4976786</v>
       </c>
@@ -8287,7 +8055,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B129" t="inlineStr">
@@ -8333,7 +8101,6 @@
           <t>in degenza</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
       <c r="L129" t="n">
         <v>45.5468804</v>
       </c>

--- a/app/src/main/assets/Pipistrelli 2024.xlsx
+++ b/app/src/main/assets/Pipistrelli 2024.xlsx
@@ -16,8 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -48,10 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -498,7 +498,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>45303</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -544,6 +544,7 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
         <v>45.6413213</v>
       </c>
@@ -562,7 +563,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -575,6 +576,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>San Lazzaro</t>
@@ -603,6 +605,7 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
         <v>45.7483873</v>
       </c>
@@ -621,7 +624,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>45371</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -634,6 +637,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -662,6 +666,7 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
         <v>45.6348591</v>
       </c>
@@ -680,7 +685,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>45385</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -726,6 +731,7 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
         <v>45.6348591</v>
       </c>
@@ -744,7 +750,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>45388</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -790,11 +796,12 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>45.6111057</v>
+        <v>45.62002</v>
       </c>
       <c r="M6" t="n">
-        <v>11.3434053</v>
+        <v>11.33649</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -808,7 +815,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>45389</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -854,11 +861,12 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>45.6111057</v>
+        <v>45.62031</v>
       </c>
       <c r="M7" t="n">
-        <v>11.3434053</v>
+        <v>11.33602</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -872,7 +880,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>45395</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -918,11 +926,12 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>45.772805</v>
+        <v>45.75382</v>
       </c>
       <c r="M8" t="n">
-        <v>11.7459248</v>
+        <v>11.72975</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -936,7 +945,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>45397</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -982,6 +991,7 @@
           <t>in degenza</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
         <v>45.5084288</v>
       </c>
@@ -1000,7 +1010,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>45398</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -1013,6 +1023,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t xml:space="preserve">Grisignano </t>
@@ -1041,12 +1052,14 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
         <v>45.5479</v>
       </c>
       <c r="M10" t="n">
         <v>11.5446</v>
       </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
           <t>VI</t>
@@ -1054,7 +1067,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>45422</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -1067,6 +1080,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -1095,6 +1109,7 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
         <v>45.6348591</v>
       </c>
@@ -1113,7 +1128,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>45423</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -1159,6 +1174,7 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
         <v>45.8461561</v>
       </c>
@@ -1177,7 +1193,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>45429</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -1223,6 +1239,7 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
         <v>45.7669109</v>
       </c>
@@ -1241,7 +1258,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>45429</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -1254,6 +1271,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>Viale Sant'Agostino</t>
@@ -1282,6 +1300,7 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
         <v>45.5276929</v>
       </c>
@@ -1300,7 +1319,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>45434</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,15 +1365,18 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>45.5063765</v>
+        <v>45.51187</v>
       </c>
       <c r="M15" t="n">
-        <v>11.5093217</v>
-      </c>
+        <v>11.52044</v>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>45436</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -1367,6 +1389,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>Viale della Pace</t>
@@ -1395,6 +1418,7 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
         <v>45.5419084</v>
       </c>
@@ -1413,7 +1437,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>45437</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -1459,6 +1483,7 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
         <v>45.8066913</v>
       </c>
@@ -1477,7 +1502,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>45446</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -1490,6 +1515,7 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>Lago di Fimon</t>
@@ -1518,15 +1544,18 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
         <v>45.4711586</v>
       </c>
       <c r="M18" t="n">
         <v>11.5436596</v>
       </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>45446</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -1539,6 +1568,7 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>Lago di Fimon</t>
@@ -1567,15 +1597,18 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
         <v>45.4711586</v>
       </c>
       <c r="M19" t="n">
         <v>11.5436596</v>
       </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>45460</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -1588,6 +1621,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>Arcugnano</t>
@@ -1616,6 +1650,7 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
         <v>45.5004723</v>
       </c>
@@ -1634,7 +1669,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>45460</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -1647,6 +1682,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>Via Col d'Echele 3</t>
@@ -1675,11 +1711,12 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="n">
-        <v>45.5561119</v>
+        <v>45.52988</v>
       </c>
       <c r="M21" t="n">
-        <v>11.5308682</v>
+        <v>11.55431</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -1693,7 +1730,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>45460</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -1706,6 +1743,7 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>Grisignano</t>
@@ -1734,12 +1772,14 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="n">
         <v>45.5479</v>
       </c>
       <c r="M22" t="n">
         <v>11.5446</v>
       </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
           <t>VI</t>
@@ -1747,7 +1787,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>45462</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -1760,6 +1800,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>Arzignano</t>
@@ -1788,6 +1829,7 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="n">
         <v>45.519292</v>
       </c>
@@ -1806,7 +1848,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>45462</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -1819,6 +1861,7 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t xml:space="preserve">Castegnero </t>
@@ -1847,6 +1890,7 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="n">
         <v>45.4424748</v>
       </c>
@@ -1865,7 +1909,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>45462</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -1878,6 +1922,7 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t xml:space="preserve">Castegnero </t>
@@ -1906,6 +1951,7 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="n">
         <v>45.4424748</v>
       </c>
@@ -1924,7 +1970,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>45462</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -1937,6 +1983,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>Verona</t>
@@ -1965,6 +2012,7 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="n">
         <v>45.4424977</v>
       </c>
@@ -1983,7 +2031,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>45462</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -1996,6 +2044,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>Schio</t>
@@ -2045,7 +2094,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>45463</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -2058,6 +2107,7 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>Thiene</t>
@@ -2086,6 +2136,7 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="n">
         <v>45.7059893</v>
       </c>
@@ -2104,7 +2155,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>45464</v>
       </c>
       <c r="B29" t="inlineStr">
@@ -2150,6 +2201,7 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="n">
         <v>45.5951803</v>
       </c>
@@ -2168,7 +2220,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>45464</v>
       </c>
       <c r="B30" t="inlineStr">
@@ -2181,6 +2233,7 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>Schio</t>
@@ -2209,6 +2262,7 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="n">
         <v>45.7113511</v>
       </c>
@@ -2227,7 +2281,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>45465</v>
       </c>
       <c r="B31" t="inlineStr">
@@ -2240,6 +2294,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>Piovene Rocchette</t>
@@ -2268,6 +2323,7 @@
           <t>in degenza</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="n">
         <v>45.7588257</v>
       </c>
@@ -2286,7 +2342,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>45466</v>
       </c>
       <c r="B32" t="inlineStr">
@@ -2299,6 +2355,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>Costozza</t>
@@ -2348,7 +2405,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>45467</v>
       </c>
       <c r="B33" t="inlineStr">
@@ -2361,6 +2418,7 @@
           <t>Pipistrellus pipistrellus</t>
         </is>
       </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>via giustiniani 79</t>
@@ -2389,11 +2447,12 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="n">
-        <v>45.5056451</v>
+        <v>45.50346</v>
       </c>
       <c r="M33" t="n">
-        <v>11.5081895</v>
+        <v>11.54117</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -2407,7 +2466,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>45467</v>
       </c>
       <c r="B34" t="inlineStr">
@@ -2420,6 +2479,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t xml:space="preserve">montecchio </t>
@@ -2469,7 +2529,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>45467</v>
       </c>
       <c r="B35" t="inlineStr">
@@ -2515,6 +2575,7 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="n">
         <v>45.5220266</v>
       </c>
@@ -2533,7 +2594,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>45467</v>
       </c>
       <c r="B36" t="inlineStr">
@@ -2579,6 +2640,7 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="n">
         <v>45.5220266</v>
       </c>
@@ -2597,7 +2659,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>45467</v>
       </c>
       <c r="B37" t="inlineStr">
@@ -2610,6 +2672,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>Verona</t>
@@ -2638,6 +2701,7 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="n">
         <v>45.4424977</v>
       </c>
@@ -2656,7 +2720,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>45467</v>
       </c>
       <c r="B38" t="inlineStr">
@@ -2669,6 +2733,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>Corso Santi Felice e Fortunato</t>
@@ -2706,9 +2771,11 @@
       <c r="M38" t="n">
         <v>11.5352125</v>
       </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>45467</v>
       </c>
       <c r="B39" t="inlineStr">
@@ -2721,6 +2788,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
           <t>Via Marchetti, 14</t>
@@ -2753,10 +2821,10 @@
         <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>45.537005</v>
+        <v>45.55621</v>
       </c>
       <c r="M39" t="n">
-        <v>11.525507</v>
+        <v>11.56012</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
@@ -2770,7 +2838,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="1" t="n">
         <v>45467</v>
       </c>
       <c r="B40" t="inlineStr">
@@ -2783,6 +2851,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>Costozza</t>
@@ -2811,15 +2880,18 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="n">
         <v>45.4709699</v>
       </c>
       <c r="M40" t="n">
         <v>11.6014322</v>
       </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="1" t="n">
         <v>45468</v>
       </c>
       <c r="B41" t="inlineStr">
@@ -2832,6 +2904,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>Via Leonardo da Vinci, 8</t>
@@ -2860,11 +2933,12 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="n">
-        <v>45.6577391</v>
+        <v>45.65934</v>
       </c>
       <c r="M41" t="n">
-        <v>11.5831095</v>
+        <v>11.58913</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
@@ -2878,7 +2952,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="1" t="n">
         <v>45468</v>
       </c>
       <c r="B42" t="inlineStr">
@@ -2891,6 +2965,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>Pove del Grappa</t>
@@ -2919,6 +2994,7 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="n">
         <v>45.7991169</v>
       </c>
@@ -2937,7 +3013,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="1" t="n">
         <v>45468</v>
       </c>
       <c r="B43" t="inlineStr">
@@ -2983,6 +3059,7 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="K43" t="inlineStr"/>
       <c r="L43" t="n">
         <v>45.697721</v>
       </c>
@@ -3001,7 +3078,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="1" t="n">
         <v>45468</v>
       </c>
       <c r="B44" t="inlineStr">
@@ -3014,6 +3091,7 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
+      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
           <t>Costozza</t>
@@ -3051,9 +3129,11 @@
       <c r="M44" t="n">
         <v>11.6014322</v>
       </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="1" t="n">
         <v>45469</v>
       </c>
       <c r="B45" t="inlineStr">
@@ -3066,6 +3146,7 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>Via Giuseppe Roi, 13</t>
@@ -3094,11 +3175,12 @@
           <t>in degenza</t>
         </is>
       </c>
+      <c r="K45" t="inlineStr"/>
       <c r="L45" t="n">
-        <v>45.4558599</v>
+        <v>45.44186</v>
       </c>
       <c r="M45" t="n">
-        <v>11.6526775</v>
+        <v>11.67789</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
@@ -3112,7 +3194,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="1" t="n">
         <v>45470</v>
       </c>
       <c r="B46" t="inlineStr">
@@ -3125,6 +3207,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
           <t>Via Piave 23</t>
@@ -3153,11 +3236,12 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="K46" t="inlineStr"/>
       <c r="L46" t="n">
-        <v>45.6180489</v>
+        <v>45.61512</v>
       </c>
       <c r="M46" t="n">
-        <v>11.4651626</v>
+        <v>11.45564</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
@@ -3171,7 +3255,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="1" t="n">
         <v>45470</v>
       </c>
       <c r="B47" t="inlineStr">
@@ -3184,6 +3268,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
           <t>Via Don A. Ziliotto, 24</t>
@@ -3202,11 +3287,13 @@
       <c r="H47" t="n">
         <v>1</v>
       </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>liberato</t>
         </is>
       </c>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="n">
         <v>45.7059893</v>
       </c>
@@ -3225,7 +3312,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="1" t="n">
         <v>45470</v>
       </c>
       <c r="B48" t="inlineStr">
@@ -3238,6 +3325,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -3287,7 +3375,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="1" t="n">
         <v>45470</v>
       </c>
       <c r="B49" t="inlineStr">
@@ -3300,6 +3388,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t>Bassano del Grappa, Vicenza</t>
@@ -3328,6 +3417,7 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="K49" t="inlineStr"/>
       <c r="L49" t="n">
         <v>45.7669109</v>
       </c>
@@ -3339,9 +3429,10 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="1" t="n">
         <v>45471</v>
       </c>
       <c r="B50" t="inlineStr">
@@ -3354,6 +3445,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -3403,7 +3495,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="1" t="n">
         <v>45471</v>
       </c>
       <c r="B51" t="inlineStr">
@@ -3416,6 +3508,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
           <t>Via Scomazzoni 12A</t>
@@ -3465,7 +3558,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="1" t="n">
         <v>45471</v>
       </c>
       <c r="B52" t="inlineStr">
@@ -3478,6 +3571,7 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
           <t>Via Monsinior Pertile</t>
@@ -3506,6 +3600,7 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="K52" t="inlineStr"/>
       <c r="L52" t="n">
         <v>45.7059893</v>
       </c>
@@ -3524,7 +3619,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="1" t="n">
         <v>45471</v>
       </c>
       <c r="B53" t="inlineStr">
@@ -3537,6 +3632,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
           <t>Via Nicolò Tommaso 12</t>
@@ -3565,6 +3661,7 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="K53" t="inlineStr"/>
       <c r="L53" t="n">
         <v>45.6861778</v>
       </c>
@@ -3583,7 +3680,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="1" t="n">
         <v>45471</v>
       </c>
       <c r="B54" t="inlineStr">
@@ -3596,6 +3693,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
           <t>Via Andrea Boccherini 23</t>
@@ -3645,7 +3743,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="1" t="n">
         <v>45471</v>
       </c>
       <c r="B55" t="inlineStr">
@@ -3658,6 +3756,7 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
           <t>Via Monsignor Pertile</t>
@@ -3686,6 +3785,7 @@
           <t>in degenza</t>
         </is>
       </c>
+      <c r="K55" t="inlineStr"/>
       <c r="L55" t="n">
         <v>45.7059893</v>
       </c>
@@ -3704,7 +3804,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="1" t="n">
         <v>45471</v>
       </c>
       <c r="B56" t="inlineStr">
@@ -3750,6 +3850,7 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="K56" t="inlineStr"/>
       <c r="L56" t="n">
         <v>45.5502771</v>
       </c>
@@ -3768,7 +3869,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="1" t="n">
         <v>45472</v>
       </c>
       <c r="B57" t="inlineStr">
@@ -3781,6 +3882,7 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
           <t>Via Lago di Tovel, 43</t>
@@ -3830,7 +3932,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="1" t="n">
         <v>45472</v>
       </c>
       <c r="B58" t="inlineStr">
@@ -3843,6 +3945,7 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
           <t>Monselice</t>
@@ -3892,7 +3995,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="1" t="n">
         <v>45472</v>
       </c>
       <c r="B59" t="inlineStr">
@@ -3905,6 +4008,7 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
           <t>Thiene</t>
@@ -3954,7 +4058,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="1" t="n">
         <v>45472</v>
       </c>
       <c r="B60" t="inlineStr">
@@ -3967,6 +4071,7 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
           <t>Grisignano</t>
@@ -4004,6 +4109,7 @@
       <c r="M60" t="n">
         <v>11.5446</v>
       </c>
+      <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr">
         <is>
           <t>VI</t>
@@ -4011,7 +4117,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="1" t="n">
         <v>45473</v>
       </c>
       <c r="B61" t="inlineStr">
@@ -4024,6 +4130,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
           <t>brogliano</t>
@@ -4052,6 +4159,7 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="n">
         <v>45.5887862</v>
       </c>
@@ -4070,7 +4178,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="1" t="n">
         <v>45473</v>
       </c>
       <c r="B62" t="inlineStr">
@@ -4083,6 +4191,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
           <t xml:space="preserve">Isola Vicentina </t>
@@ -4111,6 +4220,7 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="K62" t="inlineStr"/>
       <c r="L62" t="n">
         <v>45.6286685</v>
       </c>
@@ -4129,7 +4239,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="1" t="n">
         <v>45473</v>
       </c>
       <c r="B63" t="inlineStr">
@@ -4142,6 +4252,7 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
           <t>Marostica</t>
@@ -4170,6 +4281,7 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="K63" t="inlineStr"/>
       <c r="L63" t="n">
         <v>45.7453924</v>
       </c>
@@ -4188,7 +4300,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="1" t="n">
         <v>45474</v>
       </c>
       <c r="B64" t="inlineStr">
@@ -4201,6 +4313,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t>Sovizzo</t>
@@ -4229,6 +4342,7 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="K64" t="inlineStr"/>
       <c r="L64" t="n">
         <v>45.5280283</v>
       </c>
@@ -4247,7 +4361,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="1" t="n">
         <v>45474</v>
       </c>
       <c r="B65" t="inlineStr">
@@ -4260,6 +4374,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
           <t>Sovizzo</t>
@@ -4288,6 +4403,7 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="K65" t="inlineStr"/>
       <c r="L65" t="n">
         <v>45.5280283</v>
       </c>
@@ -4306,7 +4422,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="1" t="n">
         <v>45474</v>
       </c>
       <c r="B66" t="inlineStr">
@@ -4319,6 +4435,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
           <t>Altavilla vicentina</t>
@@ -4368,7 +4485,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="1" t="n">
         <v>45474</v>
       </c>
       <c r="B67" t="inlineStr">
@@ -4381,6 +4498,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
           <t>Bressanvido</t>
@@ -4409,6 +4527,7 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="K67" t="inlineStr"/>
       <c r="L67" t="n">
         <v>45.6459759</v>
       </c>
@@ -4427,7 +4546,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="1" t="n">
         <v>45475</v>
       </c>
       <c r="B68" t="inlineStr">
@@ -4440,6 +4559,7 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
+      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
           <t>Treviso</t>
@@ -4468,6 +4588,7 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="K68" t="inlineStr"/>
       <c r="L68" t="n">
         <v>45.8066913</v>
       </c>
@@ -4486,7 +4607,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="1" t="n">
         <v>45475</v>
       </c>
       <c r="B69" t="inlineStr">
@@ -4499,6 +4620,7 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
+      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
           <t>Via Jacopo da Ponte</t>
@@ -4527,6 +4649,7 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="K69" t="inlineStr"/>
       <c r="L69" t="n">
         <v>45.6230008</v>
       </c>
@@ -4545,7 +4668,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="1" t="n">
         <v>45474</v>
       </c>
       <c r="B70" t="inlineStr">
@@ -4558,6 +4681,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
           <t>Via Monsignor Pertile</t>
@@ -4586,6 +4710,7 @@
           <t>in degenza</t>
         </is>
       </c>
+      <c r="K70" t="inlineStr"/>
       <c r="L70" t="n">
         <v>45.7059893</v>
       </c>
@@ -4604,7 +4729,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="1" t="n">
         <v>45475</v>
       </c>
       <c r="B71" t="inlineStr">
@@ -4617,6 +4742,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
           <t>Schio</t>
@@ -4645,6 +4771,7 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="K71" t="inlineStr"/>
       <c r="L71" t="n">
         <v>45.7113511</v>
       </c>
@@ -4663,7 +4790,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="1" t="n">
         <v>45475</v>
       </c>
       <c r="B72" t="inlineStr">
@@ -4676,6 +4803,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
           <t>via bologna 33</t>
@@ -4704,6 +4832,7 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="K72" t="inlineStr"/>
       <c r="L72" t="n">
         <v>45.515467</v>
       </c>
@@ -4722,7 +4851,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="1" t="n">
         <v>45476</v>
       </c>
       <c r="B73" t="inlineStr">
@@ -4735,6 +4864,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
           <t>Arcugnano</t>
@@ -4763,6 +4893,7 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="K73" t="inlineStr"/>
       <c r="L73" t="n">
         <v>45.5004723</v>
       </c>
@@ -4781,7 +4912,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="1" t="n">
         <v>45478</v>
       </c>
       <c r="B74" t="inlineStr">
@@ -4794,6 +4925,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
           <t>Viale della Pace</t>
@@ -4822,6 +4954,7 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="K74" t="inlineStr"/>
       <c r="L74" t="n">
         <v>45.5419084</v>
       </c>
@@ -4840,7 +4973,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="1" t="n">
         <v>45479</v>
       </c>
       <c r="B75" t="inlineStr">
@@ -4853,6 +4986,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
           <t>vicenza</t>
@@ -4881,6 +5015,7 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="K75" t="inlineStr"/>
       <c r="L75" t="n">
         <v>45.6348591</v>
       </c>
@@ -4899,7 +5034,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="1" t="n">
         <v>45481</v>
       </c>
       <c r="B76" t="inlineStr">
@@ -4912,6 +5047,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
           <t>Camisano</t>
@@ -4940,6 +5076,7 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="K76" t="inlineStr"/>
       <c r="L76" t="n">
         <v>45.5479</v>
       </c>
@@ -4958,7 +5095,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="1" t="n">
         <v>45481</v>
       </c>
       <c r="B77" t="inlineStr">
@@ -4971,6 +5108,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
           <t>Strada statale Pasubio</t>
@@ -5020,7 +5158,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="1" t="n">
         <v>45481</v>
       </c>
       <c r="B78" t="inlineStr">
@@ -5033,6 +5171,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
           <t>Valdagno</t>
@@ -5082,7 +5221,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="1" t="n">
         <v>45481</v>
       </c>
       <c r="B79" t="inlineStr">
@@ -5095,6 +5234,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
           <t>Via canestrello 8</t>
@@ -5123,6 +5263,7 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="K79" t="inlineStr"/>
       <c r="L79" t="n">
         <v>45.5548982</v>
       </c>
@@ -5141,7 +5282,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="1" t="n">
         <v>45481</v>
       </c>
       <c r="B80" t="inlineStr">
@@ -5154,6 +5295,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
           <t>Via gioranzan 13</t>
@@ -5182,6 +5324,7 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="K80" t="inlineStr"/>
       <c r="L80" t="n">
         <v>45.5479</v>
       </c>
@@ -5200,7 +5343,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="1" t="n">
         <v>45482</v>
       </c>
       <c r="B81" t="inlineStr">
@@ -5213,6 +5356,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
           <t>Via Carlesse 55</t>
@@ -5241,6 +5385,7 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="K81" t="inlineStr"/>
       <c r="L81" t="n">
         <v>45.636598</v>
       </c>
@@ -5259,7 +5404,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="1" t="n">
         <v>45482</v>
       </c>
       <c r="B82" t="inlineStr">
@@ -5272,6 +5417,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
           <t>Cornedo Vicentino</t>
@@ -5321,7 +5467,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="1" t="n">
         <v>45482</v>
       </c>
       <c r="B83" t="inlineStr">
@@ -5367,6 +5513,7 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="K83" t="inlineStr"/>
       <c r="L83" t="n">
         <v>45.3317317</v>
       </c>
@@ -5385,7 +5532,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="1" t="n">
         <v>45484</v>
       </c>
       <c r="B84" t="inlineStr">
@@ -5398,6 +5545,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
           <t>Santorso</t>
@@ -5447,7 +5595,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="1" t="n">
         <v>45485</v>
       </c>
       <c r="B85" t="inlineStr">
@@ -5460,6 +5608,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
           <t>Povolaro</t>
@@ -5509,7 +5658,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="1" t="n">
         <v>45486</v>
       </c>
       <c r="B86" t="inlineStr">
@@ -5522,6 +5671,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
           <t>Longare</t>
@@ -5550,6 +5700,7 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="K86" t="inlineStr"/>
       <c r="L86" t="n">
         <v>45.4746344</v>
       </c>
@@ -5568,7 +5719,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="1" t="n">
         <v>45488</v>
       </c>
       <c r="B87" t="inlineStr">
@@ -5581,6 +5732,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
           <t>Via Oreficeria, 16</t>
@@ -5609,6 +5761,7 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="K87" t="inlineStr"/>
       <c r="L87" t="n">
         <v>45.5288639</v>
       </c>
@@ -5627,7 +5780,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="1" t="n">
         <v>45490</v>
       </c>
       <c r="B88" t="inlineStr">
@@ -5640,6 +5793,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
           <t>Malga monte Asolone</t>
@@ -5668,6 +5822,7 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="K88" t="inlineStr"/>
       <c r="L88" t="n">
         <v>45.8672973</v>
       </c>
@@ -5686,7 +5841,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="1" t="n">
         <v>45490</v>
       </c>
       <c r="B89" t="inlineStr">
@@ -5699,6 +5854,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
           <t>Via Aurelio dall'acqua 119</t>
@@ -5727,6 +5883,7 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="K89" t="inlineStr"/>
       <c r="L89" t="n">
         <v>45.5678021</v>
       </c>
@@ -5745,7 +5902,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="1" t="n">
         <v>45490</v>
       </c>
       <c r="B90" t="inlineStr">
@@ -5758,6 +5915,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
           <t>Via Tecchio</t>
@@ -5807,7 +5965,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="1" t="n">
         <v>45490</v>
       </c>
       <c r="B91" t="inlineStr">
@@ -5820,6 +5978,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
           <t>Via Marnian</t>
@@ -5848,6 +6007,7 @@
           <t>in degenza</t>
         </is>
       </c>
+      <c r="K91" t="inlineStr"/>
       <c r="L91" t="n">
         <v>45.7669109</v>
       </c>
@@ -5866,7 +6026,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="1" t="n">
         <v>45492</v>
       </c>
       <c r="B92" t="inlineStr">
@@ -5879,6 +6039,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
           <t>Via mottarella 17</t>
@@ -5907,6 +6068,7 @@
           <t>in degenza</t>
         </is>
       </c>
+      <c r="K92" t="inlineStr"/>
       <c r="L92" t="n">
         <v>45.3446852</v>
       </c>
@@ -5925,7 +6087,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="1" t="n">
         <v>45494</v>
       </c>
       <c r="B93" t="inlineStr">
@@ -5938,6 +6100,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
           <t>Vicolo xx settembre 9</t>
@@ -5966,6 +6129,7 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="K93" t="inlineStr"/>
       <c r="L93" t="n">
         <v>45.7683298</v>
       </c>
@@ -5984,7 +6148,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="1" t="n">
         <v>45497</v>
       </c>
       <c r="B94" t="inlineStr">
@@ -5997,6 +6161,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
           <t>Bassano</t>
@@ -6039,9 +6204,10 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O94" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="1" t="n">
         <v>45499</v>
       </c>
       <c r="B95" t="inlineStr">
@@ -6054,6 +6220,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
           <t>Calvene</t>
@@ -6082,6 +6249,7 @@
           <t>in degenza</t>
         </is>
       </c>
+      <c r="K95" t="inlineStr"/>
       <c r="L95" t="n">
         <v>45.7659086</v>
       </c>
@@ -6100,7 +6268,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="1" t="n">
         <v>45502</v>
       </c>
       <c r="B96" t="inlineStr">
@@ -6113,6 +6281,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
           <t>Lusiana</t>
@@ -6141,15 +6310,18 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="K96" t="inlineStr"/>
       <c r="L96" t="n">
         <v>45.7851934</v>
       </c>
       <c r="M96" t="n">
         <v>11.576369</v>
       </c>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="1" t="n">
         <v>45503</v>
       </c>
       <c r="B97" t="inlineStr">
@@ -6162,6 +6334,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
           <t>Via dei laghi 20</t>
@@ -6190,6 +6363,7 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="K97" t="inlineStr"/>
       <c r="L97" t="n">
         <v>45.5211218</v>
       </c>
@@ -6208,7 +6382,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="1" t="n">
         <v>45503</v>
       </c>
       <c r="B98" t="inlineStr">
@@ -6221,6 +6395,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
           <t>Via Barco 21</t>
@@ -6249,6 +6424,7 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="K98" t="inlineStr"/>
       <c r="L98" t="n">
         <v>45.6077149</v>
       </c>
@@ -6267,7 +6443,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="1" t="n">
         <v>45505</v>
       </c>
       <c r="B99" t="inlineStr">
@@ -6280,6 +6456,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
           <t>Via odone 18 a</t>
@@ -6308,6 +6485,7 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="K99" t="inlineStr"/>
       <c r="L99" t="n">
         <v>45.5479</v>
       </c>
@@ -6326,7 +6504,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="1" t="n">
         <v>45505</v>
       </c>
       <c r="B100" t="inlineStr">
@@ -6372,6 +6550,7 @@
           <t>in degenza</t>
         </is>
       </c>
+      <c r="K100" t="inlineStr"/>
       <c r="L100" t="n">
         <v>45.7962374</v>
       </c>
@@ -6390,7 +6569,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n">
+      <c r="A101" s="1" t="n">
         <v>45511</v>
       </c>
       <c r="B101" t="inlineStr">
@@ -6403,6 +6582,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
           <t>Valdagno</t>
@@ -6431,6 +6611,7 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="K101" t="inlineStr"/>
       <c r="L101" t="n">
         <v>45.6413213</v>
       </c>
@@ -6449,7 +6630,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="1" t="n">
         <v>45520</v>
       </c>
       <c r="B102" t="inlineStr">
@@ -6462,6 +6643,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
           <t>Via monte oro 33</t>
@@ -6490,6 +6672,7 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="K102" t="inlineStr"/>
       <c r="L102" t="n">
         <v>45.7942477</v>
       </c>
@@ -6508,7 +6691,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n">
+      <c r="A103" s="1" t="n">
         <v>45525</v>
       </c>
       <c r="B103" t="inlineStr">
@@ -6521,6 +6704,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
           <t>Valdagno</t>
@@ -6549,6 +6733,7 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="K103" t="inlineStr"/>
       <c r="L103" t="n">
         <v>45.6413213</v>
       </c>
@@ -6567,7 +6752,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n">
+      <c r="A104" s="1" t="n">
         <v>45533</v>
       </c>
       <c r="B104" t="inlineStr">
@@ -6613,6 +6798,7 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="K104" t="inlineStr"/>
       <c r="L104" t="n">
         <v>45.7669109</v>
       </c>
@@ -6631,7 +6817,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="n">
+      <c r="A105" s="1" t="n">
         <v>45533</v>
       </c>
       <c r="B105" t="inlineStr">
@@ -6644,6 +6830,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
           <t>Via Marco Marinoni 28</t>
@@ -6693,7 +6880,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n">
+      <c r="A106" s="1" t="n">
         <v>45537</v>
       </c>
       <c r="B106" t="inlineStr">
@@ -6706,6 +6893,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -6734,6 +6922,7 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="K106" t="inlineStr"/>
       <c r="L106" t="n">
         <v>45.6348591</v>
       </c>
@@ -6752,7 +6941,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n">
+      <c r="A107" s="1" t="n">
         <v>45540</v>
       </c>
       <c r="B107" t="inlineStr">
@@ -6765,6 +6954,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
           <t>Dueville</t>
@@ -6793,6 +6983,7 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="K107" t="inlineStr"/>
       <c r="L107" t="n">
         <v>45.6355174</v>
       </c>
@@ -6811,7 +7002,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n">
+      <c r="A108" s="1" t="n">
         <v>45544</v>
       </c>
       <c r="B108" t="inlineStr">
@@ -6824,6 +7015,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
           <t>Via Oreficeria, 16</t>
@@ -6852,6 +7044,7 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="K108" t="inlineStr"/>
       <c r="L108" t="n">
         <v>45.5288639</v>
       </c>
@@ -6870,7 +7063,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n">
+      <c r="A109" s="1" t="n">
         <v>45544</v>
       </c>
       <c r="B109" t="inlineStr">
@@ -6883,6 +7076,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
           <t>Arcugnano</t>
@@ -6911,6 +7105,7 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="K109" t="inlineStr"/>
       <c r="L109" t="n">
         <v>45.5004723</v>
       </c>
@@ -6929,7 +7124,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n">
+      <c r="A110" s="1" t="n">
         <v>45544</v>
       </c>
       <c r="B110" t="inlineStr">
@@ -6942,6 +7137,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
           <t>Via Monte Pasubio 96a</t>
@@ -6970,6 +7166,7 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="K110" t="inlineStr"/>
       <c r="L110" t="n">
         <v>45.7209364</v>
       </c>
@@ -6988,7 +7185,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n">
+      <c r="A111" s="1" t="n">
         <v>45547</v>
       </c>
       <c r="B111" t="inlineStr">
@@ -7034,6 +7231,7 @@
           <t>in degenza</t>
         </is>
       </c>
+      <c r="K111" t="inlineStr"/>
       <c r="L111" t="n">
         <v>45.5269679</v>
       </c>
@@ -7052,7 +7250,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n">
+      <c r="A112" s="1" t="n">
         <v>45552</v>
       </c>
       <c r="B112" t="inlineStr">
@@ -7065,6 +7263,7 @@
           <t>Plecotus sp.</t>
         </is>
       </c>
+      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
           <t xml:space="preserve">Bassano del Grappa </t>
@@ -7093,6 +7292,7 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="K112" t="inlineStr"/>
       <c r="L112" t="n">
         <v>45.7669109</v>
       </c>
@@ -7111,7 +7311,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n">
+      <c r="A113" s="1" t="n">
         <v>45553</v>
       </c>
       <c r="B113" t="inlineStr">
@@ -7124,6 +7324,7 @@
           <t>Plecotus Macrobullaris</t>
         </is>
       </c>
+      <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
           <t>Santorso</t>
@@ -7152,6 +7353,7 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="K113" t="inlineStr"/>
       <c r="L113" t="n">
         <v>45.7372986</v>
       </c>
@@ -7170,7 +7372,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n">
+      <c r="A114" s="1" t="n">
         <v>45556</v>
       </c>
       <c r="B114" t="inlineStr">
@@ -7216,6 +7418,7 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="K114" t="inlineStr"/>
       <c r="L114" t="n">
         <v>45.5419084</v>
       </c>
@@ -7234,7 +7437,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n">
+      <c r="A115" s="1" t="n">
         <v>45557</v>
       </c>
       <c r="B115" t="inlineStr">
@@ -7247,6 +7450,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
           <t>Via San Niccolò 53</t>
@@ -7265,20 +7469,24 @@
       <c r="H115" t="n">
         <v>1</v>
       </c>
+      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
           <t>in degenza</t>
         </is>
       </c>
+      <c r="K115" t="inlineStr"/>
       <c r="L115" t="n">
         <v>45.453842</v>
       </c>
       <c r="M115" t="n">
         <v>11.5551735</v>
       </c>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n">
+      <c r="A116" s="1" t="n">
         <v>45558</v>
       </c>
       <c r="B116" t="inlineStr">
@@ -7291,6 +7499,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
           <t xml:space="preserve">Dueville </t>
@@ -7319,6 +7528,7 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="K116" t="inlineStr"/>
       <c r="L116" t="n">
         <v>45.6355174</v>
       </c>
@@ -7337,7 +7547,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n">
+      <c r="A117" s="1" t="n">
         <v>45560</v>
       </c>
       <c r="B117" t="inlineStr">
@@ -7383,6 +7593,7 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="K117" t="inlineStr"/>
       <c r="L117" t="n">
         <v>45.7059893</v>
       </c>
@@ -7401,7 +7612,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n">
+      <c r="A118" s="1" t="n">
         <v>45562</v>
       </c>
       <c r="B118" t="inlineStr">
@@ -7447,6 +7658,7 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="K118" t="inlineStr"/>
       <c r="L118" t="n">
         <v>45.6073305</v>
       </c>
@@ -7465,7 +7677,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="A119" s="1" t="n">
         <v>45565</v>
       </c>
       <c r="B119" t="inlineStr">
@@ -7511,6 +7723,7 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="K119" t="inlineStr"/>
       <c r="L119" t="n">
         <v>45.7669109</v>
       </c>
@@ -7529,7 +7742,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n">
+      <c r="A120" s="1" t="n">
         <v>45566</v>
       </c>
       <c r="B120" t="inlineStr">
@@ -7542,6 +7755,7 @@
           <t>Pipistrellus pipistrellus</t>
         </is>
       </c>
+      <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -7570,6 +7784,7 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="K120" t="inlineStr"/>
       <c r="L120" t="n">
         <v>45.6348591</v>
       </c>
@@ -7588,7 +7803,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n">
+      <c r="A121" s="1" t="n">
         <v>45572</v>
       </c>
       <c r="B121" t="inlineStr">
@@ -7601,6 +7816,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
           <t>Via lago di fimon 63</t>
@@ -7629,6 +7845,7 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="K121" t="inlineStr"/>
       <c r="L121" t="n">
         <v>45.4544981</v>
       </c>
@@ -7647,7 +7864,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n">
+      <c r="A122" s="1" t="n">
         <v>45574</v>
       </c>
       <c r="B122" t="inlineStr">
@@ -7660,6 +7877,7 @@
           <t>Tadarida teniotis</t>
         </is>
       </c>
+      <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -7688,6 +7906,7 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="K122" t="inlineStr"/>
       <c r="L122" t="n">
         <v>45.6348591</v>
       </c>
@@ -7706,7 +7925,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n">
+      <c r="A123" s="1" t="n">
         <v>45583</v>
       </c>
       <c r="B123" t="inlineStr">
@@ -7719,6 +7938,7 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
+      <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
           <t>Lonigo</t>
@@ -7747,6 +7967,7 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="K123" t="inlineStr"/>
       <c r="L123" t="n">
         <v>45.3881155</v>
       </c>
@@ -7765,7 +7986,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n">
+      <c r="A124" s="1" t="n">
         <v>45584</v>
       </c>
       <c r="B124" t="inlineStr">
@@ -7811,6 +8032,7 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="K124" t="inlineStr"/>
       <c r="L124" t="n">
         <v>45.7113511</v>
       </c>
@@ -7829,7 +8051,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="n">
+      <c r="A125" s="1" t="n">
         <v>45586</v>
       </c>
       <c r="B125" t="inlineStr">
@@ -7842,6 +8064,7 @@
           <t>Pipistrello</t>
         </is>
       </c>
+      <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -7870,6 +8093,7 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="K125" t="inlineStr"/>
       <c r="L125" t="n">
         <v>45.6348591</v>
       </c>
@@ -7888,7 +8112,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n">
+      <c r="A126" s="1" t="n">
         <v>45591</v>
       </c>
       <c r="B126" t="inlineStr">
@@ -7934,6 +8158,7 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="K126" t="inlineStr"/>
       <c r="L126" t="n">
         <v>45.5422473</v>
       </c>
@@ -7952,7 +8177,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n">
+      <c r="A127" s="1" t="n">
         <v>45599</v>
       </c>
       <c r="B127" t="inlineStr">
@@ -7965,6 +8190,7 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
+      <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -7993,6 +8219,7 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="K127" t="inlineStr"/>
       <c r="L127" t="n">
         <v>45.6348591</v>
       </c>
@@ -8011,7 +8238,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n">
+      <c r="A128" s="1" t="n">
         <v>45607</v>
       </c>
       <c r="B128" t="inlineStr">
@@ -8057,6 +8284,7 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="K128" t="inlineStr"/>
       <c r="L128" t="n">
         <v>45.4976786</v>
       </c>
@@ -8075,7 +8303,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="n">
+      <c r="A129" s="1" t="n">
         <v>45657</v>
       </c>
       <c r="B129" t="inlineStr">
@@ -8121,6 +8349,7 @@
           <t>in degenza</t>
         </is>
       </c>
+      <c r="K129" t="inlineStr"/>
       <c r="L129" t="n">
         <v>45.5468804</v>
       </c>

--- a/app/src/main/assets/Pipistrelli 2024.xlsx
+++ b/app/src/main/assets/Pipistrelli 2024.xlsx
@@ -798,10 +798,10 @@
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>45.62002</v>
+        <v>45.6111057</v>
       </c>
       <c r="M6" t="n">
-        <v>11.33649</v>
+        <v>11.3434053</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -863,10 +863,10 @@
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>45.62031</v>
+        <v>45.6111057</v>
       </c>
       <c r="M7" t="n">
-        <v>11.33602</v>
+        <v>11.3434053</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -928,10 +928,10 @@
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>45.75382</v>
+        <v>45.772805</v>
       </c>
       <c r="M8" t="n">
-        <v>11.72975</v>
+        <v>11.7459248</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -1367,10 +1367,10 @@
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>45.51187</v>
+        <v>45.5063765</v>
       </c>
       <c r="M15" t="n">
-        <v>11.52044</v>
+        <v>11.5093217</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
@@ -1713,10 +1713,10 @@
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="n">
-        <v>45.52988</v>
+        <v>45.5561119</v>
       </c>
       <c r="M21" t="n">
-        <v>11.55431</v>
+        <v>11.5308682</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2449,10 +2449,10 @@
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="n">
-        <v>45.50346</v>
+        <v>45.5056451</v>
       </c>
       <c r="M33" t="n">
-        <v>11.54117</v>
+        <v>11.5081895</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -2821,10 +2821,10 @@
         <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>45.55621</v>
+        <v>45.537005</v>
       </c>
       <c r="M39" t="n">
-        <v>11.56012</v>
+        <v>11.525507</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
@@ -2935,10 +2935,10 @@
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="n">
-        <v>45.65934</v>
+        <v>45.6577391</v>
       </c>
       <c r="M41" t="n">
-        <v>11.58913</v>
+        <v>11.5831095</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
@@ -3177,10 +3177,10 @@
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="n">
-        <v>45.44186</v>
+        <v>45.4558599</v>
       </c>
       <c r="M45" t="n">
-        <v>11.67789</v>
+        <v>11.6526775</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
@@ -3238,10 +3238,10 @@
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="n">
-        <v>45.61512</v>
+        <v>45.6180489</v>
       </c>
       <c r="M46" t="n">
-        <v>11.45564</v>
+        <v>11.4651626</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
@@ -3295,10 +3295,10 @@
       </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="n">
-        <v>45.71185</v>
+        <v>45.7059893</v>
       </c>
       <c r="M47" t="n">
-        <v>11.49258</v>
+        <v>11.4797197</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
@@ -3541,10 +3541,10 @@
         <v>2</v>
       </c>
       <c r="L51" t="n">
-        <v>45.76346</v>
+        <v>45.7617885</v>
       </c>
       <c r="M51" t="n">
-        <v>11.69022</v>
+        <v>11.6904038</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
@@ -3663,10 +3663,10 @@
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="n">
-        <v>45.68884</v>
+        <v>45.6861778</v>
       </c>
       <c r="M53" t="n">
-        <v>11.72458</v>
+        <v>11.7041837</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
@@ -3726,10 +3726,10 @@
         <v>1</v>
       </c>
       <c r="L54" t="n">
-        <v>45.56834</v>
+        <v>45.6348591</v>
       </c>
       <c r="M54" t="n">
-        <v>11.53066</v>
+        <v>11.4063543</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
@@ -3852,10 +3852,10 @@
       </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="n">
-        <v>45.54921</v>
+        <v>45.5502771</v>
       </c>
       <c r="M56" t="n">
-        <v>11.55171</v>
+        <v>11.5516142</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
@@ -3915,10 +3915,10 @@
         <v>3</v>
       </c>
       <c r="L57" t="n">
-        <v>45.51862</v>
+        <v>45.5171627</v>
       </c>
       <c r="M57" t="n">
-        <v>11.45803</v>
+        <v>11.460852</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>brogliano</t>
+          <t>Brogliano</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4834,10 +4834,10 @@
       </c>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="n">
-        <v>45.52097</v>
+        <v>45.515467</v>
       </c>
       <c r="M72" t="n">
-        <v>11.46467</v>
+        <v>11.4849202</v>
       </c>
       <c r="N72" t="inlineStr">
         <is>
@@ -5265,10 +5265,10 @@
       </c>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="n">
-        <v>45.55627</v>
+        <v>45.5548982</v>
       </c>
       <c r="M79" t="n">
-        <v>11.46513</v>
+        <v>11.4719785</v>
       </c>
       <c r="N79" t="inlineStr">
         <is>
@@ -5326,10 +5326,10 @@
       </c>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="n">
-        <v>45.52628</v>
+        <v>45.5479</v>
       </c>
       <c r="M80" t="n">
-        <v>11.71618</v>
+        <v>11.5446</v>
       </c>
       <c r="N80" t="inlineStr">
         <is>
@@ -5387,10 +5387,10 @@
       </c>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="n">
-        <v>45.63229</v>
+        <v>45.636598</v>
       </c>
       <c r="M81" t="n">
-        <v>11.55835</v>
+        <v>11.5422153</v>
       </c>
       <c r="N81" t="inlineStr">
         <is>
@@ -5515,10 +5515,10 @@
       </c>
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="n">
-        <v>45.31683</v>
+        <v>45.3317317</v>
       </c>
       <c r="M83" t="n">
-        <v>11.58302</v>
+        <v>11.5714548</v>
       </c>
       <c r="N83" t="inlineStr">
         <is>
@@ -5763,10 +5763,10 @@
       </c>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="n">
-        <v>45.52901</v>
+        <v>45.5288639</v>
       </c>
       <c r="M87" t="n">
-        <v>11.50731</v>
+        <v>11.5073739</v>
       </c>
       <c r="N87" t="inlineStr">
         <is>
@@ -5885,10 +5885,10 @@
       </c>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="n">
-        <v>45.53981</v>
+        <v>45.5678021</v>
       </c>
       <c r="M89" t="n">
-        <v>11.56447</v>
+        <v>11.5752439</v>
       </c>
       <c r="N89" t="inlineStr">
         <is>
@@ -6070,10 +6070,10 @@
       </c>
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="n">
-        <v>45.34441</v>
+        <v>45.3446852</v>
       </c>
       <c r="M92" t="n">
-        <v>11.45888</v>
+        <v>11.4583737</v>
       </c>
       <c r="N92" t="inlineStr">
         <is>
@@ -6131,10 +6131,10 @@
       </c>
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="n">
-        <v>45.76611</v>
+        <v>45.7683298</v>
       </c>
       <c r="M93" t="n">
-        <v>11.73358</v>
+        <v>11.7367741</v>
       </c>
       <c r="N93" t="inlineStr">
         <is>
@@ -6164,12 +6164,12 @@
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Bassano</t>
+          <t>Bassano Del Grappa</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Bassano</t>
+          <t>Bassano Del Grappa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -6194,10 +6194,10 @@
         <v>1</v>
       </c>
       <c r="L94" t="n">
-        <v>50.7878642</v>
+        <v>45.766911</v>
       </c>
       <c r="M94" t="n">
-        <v>-112.4658831</v>
+        <v>11.734347</v>
       </c>
       <c r="N94" t="inlineStr">
         <is>
@@ -6365,10 +6365,10 @@
       </c>
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="n">
-        <v>45.51172</v>
+        <v>45.5211218</v>
       </c>
       <c r="M97" t="n">
-        <v>11.46955</v>
+        <v>11.463433</v>
       </c>
       <c r="N97" t="inlineStr">
         <is>
@@ -6426,10 +6426,10 @@
       </c>
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="n">
-        <v>45.61759</v>
+        <v>45.6077149</v>
       </c>
       <c r="M98" t="n">
-        <v>11.52401</v>
+        <v>11.5097243</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -6487,10 +6487,10 @@
       </c>
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="n">
-        <v>45.4332</v>
+        <v>45.5479</v>
       </c>
       <c r="M99" t="n">
-        <v>11.58153</v>
+        <v>11.5446</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
@@ -6674,10 +6674,10 @@
       </c>
       <c r="K102" t="inlineStr"/>
       <c r="L102" t="n">
-        <v>45.80345</v>
+        <v>45.7942477</v>
       </c>
       <c r="M102" t="n">
-        <v>11.72953</v>
+        <v>11.7321801</v>
       </c>
       <c r="N102" t="inlineStr">
         <is>
@@ -6863,10 +6863,10 @@
         <v>1</v>
       </c>
       <c r="L105" t="n">
-        <v>45.41212</v>
+        <v>45.4083415</v>
       </c>
       <c r="M105" t="n">
-        <v>11.54351</v>
+        <v>11.5676593</v>
       </c>
       <c r="N105" t="inlineStr">
         <is>
@@ -7046,10 +7046,10 @@
       </c>
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="n">
-        <v>45.52901</v>
+        <v>45.5288639</v>
       </c>
       <c r="M108" t="n">
-        <v>11.50731</v>
+        <v>11.5073739</v>
       </c>
       <c r="N108" t="inlineStr">
         <is>
@@ -7168,10 +7168,10 @@
       </c>
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="n">
-        <v>45.72242</v>
+        <v>45.7209364</v>
       </c>
       <c r="M110" t="n">
-        <v>11.45524</v>
+        <v>11.4422352</v>
       </c>
       <c r="N110" t="inlineStr">
         <is>
@@ -7477,10 +7477,10 @@
       </c>
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="n">
-        <v>45.47458</v>
+        <v>45.453842</v>
       </c>
       <c r="M115" t="n">
-        <v>11.56456</v>
+        <v>11.5551735</v>
       </c>
       <c r="N115" t="inlineStr"/>
       <c r="O115" t="inlineStr"/>
@@ -7847,10 +7847,10 @@
       </c>
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="n">
-        <v>45.46824</v>
+        <v>45.4544981</v>
       </c>
       <c r="M121" t="n">
-        <v>11.54315</v>
+        <v>11.5411704</v>
       </c>
       <c r="N121" t="inlineStr">
         <is>
@@ -8160,10 +8160,10 @@
       </c>
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="n">
-        <v>45.54289</v>
+        <v>45.5422473</v>
       </c>
       <c r="M126" t="n">
-        <v>11.55013</v>
+        <v>11.5503382</v>
       </c>
       <c r="N126" t="inlineStr">
         <is>
@@ -8286,10 +8286,10 @@
       </c>
       <c r="K128" t="inlineStr"/>
       <c r="L128" t="n">
-        <v>45.49842</v>
+        <v>45.4976786</v>
       </c>
       <c r="M128" t="n">
-        <v>11.53678</v>
+        <v>11.5381176</v>
       </c>
       <c r="N128" t="inlineStr">
         <is>

--- a/app/src/main/assets/Pipistrelli 2024.xlsx
+++ b/app/src/main/assets/Pipistrelli 2024.xlsx
@@ -6194,10 +6194,10 @@
         <v>1</v>
       </c>
       <c r="L94" t="n">
-        <v>45.766911</v>
+        <v>50.7878642</v>
       </c>
       <c r="M94" t="n">
-        <v>11.734347</v>
+        <v>-112.4658831</v>
       </c>
       <c r="N94" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Villabalzana </t>
+          <t>Arcugnano (Villabalzana)</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -7482,8 +7482,16 @@
       <c r="M115" t="n">
         <v>11.5551735</v>
       </c>
-      <c r="N115" t="inlineStr"/>
-      <c r="O115" t="inlineStr"/>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
